--- a/data/prices/current_prices.xlsx
+++ b/data/prices/current_prices.xlsx
@@ -5,25 +5,27 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haixia.lu\Desktop\20260803\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D盘\卢海霞\0-芯片工作\17-芯片实际成本\2026年\20260901\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10600"/>
+    <workbookView windowWidth="25600" windowHeight="10600" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PO" sheetId="1" r:id="rId1"/>
-    <sheet name="价目表0701" sheetId="7" r:id="rId2"/>
-    <sheet name="价目表名称" sheetId="4" r:id="rId3"/>
-    <sheet name="历史" sheetId="5" state="hidden" r:id="rId4"/>
-    <sheet name="一揽子" sheetId="6" state="hidden" r:id="rId5"/>
-    <sheet name="型号" sheetId="9" r:id="rId6"/>
+    <sheet name="chanhua芯片价格" sheetId="1" r:id="rId1"/>
+    <sheet name="galta芯片价格 " sheetId="10" r:id="rId2"/>
+    <sheet name="价目表0701" sheetId="7" r:id="rId3"/>
+    <sheet name="价目表名称" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="历史" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="一揽子" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="型号" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PO!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">价目表0701!$A$1:$S$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">历史!$A$2:$R$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">一揽子!$A$2:$BD$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">chanhua芯片价格!$A$1:$L$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'galta芯片价格 '!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">价目表0701!$A$1:$S$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">历史!$A$2:$R$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">一揽子!$A$2:$BD$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -75,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="201">
   <si>
     <t>芯片型号</t>
   </si>
@@ -182,9 +184,6 @@
     <t>BM1373</t>
   </si>
   <si>
-    <t>更新</t>
-  </si>
-  <si>
     <t>BM1493</t>
   </si>
   <si>
@@ -195,6 +194,12 @@
   </si>
   <si>
     <t>BM2560</t>
+  </si>
+  <si>
+    <t>1227——&gt;SG/HK</t>
+  </si>
+  <si>
+    <t>更新了</t>
   </si>
   <si>
     <t>产品上下文</t>
@@ -690,7 +695,7 @@
     <numFmt numFmtId="177" formatCode="0.0000_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -705,11 +710,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
@@ -717,7 +717,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -729,13 +728,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="等线"/>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="Segoe UI"/>
+      <b/>
+      <sz val="11"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -883,18 +883,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -910,12 +910,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1239,13 +1233,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1254,37 +1251,37 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1299,77 +1296,74 @@
     <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1386,63 +1380,49 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1769,59 +1749,58 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="9.5" style="13" customWidth="1"/>
     <col min="2" max="2" width="13.3333333333333" style="12" customWidth="1"/>
     <col min="3" max="3" width="16.25" style="12" customWidth="1"/>
-    <col min="4" max="4" width="27.0416666666667" style="17" customWidth="1"/>
+    <col min="4" max="4" width="27.0416666666667" style="14" customWidth="1"/>
     <col min="5" max="6" width="8.83333333333333" style="13"/>
-    <col min="7" max="7" width="8.83333333333333" style="14" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.4166666666667" style="14" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.83333333333333" style="21" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.4166666666667" style="21" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="12.775" style="13" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="8.83333333333333" style="13" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="8.83333333333333" style="18" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="8.83333333333333" style="13" hidden="1" customWidth="1"/>
-    <col min="13" max="15" width="8.83333333333333" style="13" customWidth="1"/>
+    <col min="11" max="11" width="8.83333333333333" style="22" hidden="1" customWidth="1"/>
+    <col min="12" max="15" width="8.83333333333333" style="13" customWidth="1"/>
     <col min="16" max="16384" width="8.83333333333333" style="13"/>
   </cols>
   <sheetData>
     <row r="1" s="12" customFormat="1" ht="12" customHeight="1" spans="1:11">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19" t="s">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="22" t="s">
+      <c r="G1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="24"/>
+      <c r="K1" s="26"/>
     </row>
     <row r="2" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="B2" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="19">
         <v>3.7699</v>
       </c>
       <c r="G2" s="28" t="s">
@@ -1838,22 +1817,22 @@
         <f>A2=G2</f>
         <v>1</v>
       </c>
-      <c r="K2" s="18">
+      <c r="K2" s="22">
         <f>D2-I2</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C3" s="26" t="s">
+      <c r="B3" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="19">
         <v>57.6365</v>
       </c>
       <c r="E3" s="13"/>
@@ -1864,29 +1843,29 @@
         <v>57.6364608607962</v>
       </c>
       <c r="I3" s="13">
-        <f t="shared" ref="I3:I32" si="0">ROUND(H3,4)</f>
+        <f t="shared" ref="I3:I33" si="0">ROUND(H3,4)</f>
         <v>57.6365</v>
       </c>
       <c r="J3" s="13" t="b">
-        <f t="shared" ref="J3:J32" si="1">A3=G3</f>
+        <f t="shared" ref="J3:J33" si="1">A3=G3</f>
         <v>1</v>
       </c>
-      <c r="K3" s="18">
-        <f t="shared" ref="K3:K32" si="2">D3-I3</f>
+      <c r="K3" s="22">
+        <f t="shared" ref="K3:K33" si="2">D3-I3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C4" s="26" t="s">
+      <c r="B4" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="19">
         <v>2.4828</v>
       </c>
       <c r="G4" s="28" t="s">
@@ -1903,22 +1882,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K4" s="18">
+      <c r="K4" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C5" s="26" t="s">
+      <c r="B5" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="19">
         <v>4.0901</v>
       </c>
       <c r="G5" s="28" t="s">
@@ -1935,22 +1914,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K5" s="18">
+      <c r="K5" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C6" s="26" t="s">
+      <c r="B6" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="19">
         <v>5.0536</v>
       </c>
       <c r="G6" s="28" t="s">
@@ -1967,22 +1946,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K6" s="18">
+      <c r="K6" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C7" s="26" t="s">
+      <c r="B7" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="19">
         <v>3.5349</v>
       </c>
       <c r="G7" s="28" t="s">
@@ -1999,22 +1978,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K7" s="18">
+      <c r="K7" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C8" s="26" t="s">
+      <c r="B8" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="19">
         <v>200.2487</v>
       </c>
       <c r="G8" s="28" t="s">
@@ -2031,22 +2010,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K8" s="18">
+      <c r="K8" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C9" s="26" t="s">
+      <c r="B9" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="19">
         <v>5.2113</v>
       </c>
       <c r="G9" s="28" t="s">
@@ -2063,22 +2042,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C10" s="26" t="s">
+      <c r="B10" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="19">
         <v>3.7914</v>
       </c>
       <c r="G10" s="28" t="s">
@@ -2095,22 +2074,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K10" s="18">
+      <c r="K10" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C11" s="26" t="s">
+      <c r="B11" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C11" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="19">
         <v>3.4623</v>
       </c>
       <c r="G11" s="28" t="s">
@@ -2127,22 +2106,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C12" s="26" t="s">
+      <c r="B12" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="19">
         <v>3.4712</v>
       </c>
       <c r="G12" s="28" t="s">
@@ -2159,22 +2138,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K12" s="18">
+      <c r="K12" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C13" s="26" t="s">
+      <c r="B13" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="19">
         <v>3.4712</v>
       </c>
       <c r="G13" s="28" t="s">
@@ -2191,22 +2170,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K13" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C14" s="26" t="s">
+      <c r="B14" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="19">
         <v>3.4712</v>
       </c>
       <c r="G14" s="28" t="s">
@@ -2223,22 +2202,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K14" s="18">
+      <c r="K14" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C15" s="26" t="s">
+      <c r="B15" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="19">
         <v>3.4712</v>
       </c>
       <c r="G15" s="28" t="s">
@@ -2255,22 +2234,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K15" s="18">
+      <c r="K15" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C16" s="26" t="s">
+      <c r="B16" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="19">
         <v>3.4712</v>
       </c>
       <c r="G16" s="28" t="s">
@@ -2287,22 +2266,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K16" s="18">
+      <c r="K16" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" s="13" customFormat="1" ht="14" spans="1:12">
-      <c r="A17" s="25" t="s">
+    <row r="17" s="13" customFormat="1" ht="14" spans="1:11">
+      <c r="A17" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="B17" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C17" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="19">
         <v>250.5673</v>
       </c>
       <c r="G17" s="28" t="s">
@@ -2319,22 +2298,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K17" s="18">
+      <c r="K17" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" s="13" customFormat="1" ht="14" spans="1:12">
-      <c r="A18" s="25" t="s">
+    <row r="18" s="13" customFormat="1" ht="14" spans="1:11">
+      <c r="A18" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C18" s="26" t="s">
+      <c r="B18" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="19">
         <v>55.1336</v>
       </c>
       <c r="G18" s="28" t="s">
@@ -2351,22 +2330,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K18" s="18">
+      <c r="K18" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" s="13" customFormat="1" ht="14" spans="1:12">
-      <c r="A19" s="25" t="s">
+    <row r="19" s="13" customFormat="1" ht="14" spans="1:11">
+      <c r="A19" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C19" s="26" t="s">
+      <c r="B19" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="19">
         <v>2324.8445</v>
       </c>
       <c r="G19" s="28" t="s">
@@ -2383,22 +2362,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K19" s="18">
+      <c r="K19" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" s="13" customFormat="1" ht="14" spans="1:12">
-      <c r="A20" s="25" t="s">
+    <row r="20" s="13" customFormat="1" ht="14" spans="1:11">
+      <c r="A20" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C20" s="26" t="s">
+      <c r="B20" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="19">
         <v>2.2925</v>
       </c>
       <c r="G20" s="28" t="s">
@@ -2415,22 +2394,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K20" s="18">
+      <c r="K20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" s="13" customFormat="1" ht="14" spans="1:12">
-      <c r="A21" s="25" t="s">
+    <row r="21" s="13" customFormat="1" ht="14" spans="1:11">
+      <c r="A21" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C21" s="26" t="s">
+      <c r="B21" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="19">
         <v>8.4438</v>
       </c>
       <c r="E21" s="13"/>
@@ -2448,22 +2427,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K21" s="18">
+      <c r="K21" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" s="13" customFormat="1" ht="14" spans="1:12">
-      <c r="A22" s="25" t="s">
+    <row r="22" s="13" customFormat="1" ht="14" spans="1:11">
+      <c r="A22" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C22" s="26" t="s">
+      <c r="B22" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C22" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="19">
         <v>2.9837</v>
       </c>
       <c r="G22" s="28" t="s">
@@ -2480,19 +2459,19 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K22" s="18">
+      <c r="K22" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" s="14" customFormat="1" ht="14" spans="1:12">
+    <row r="23" s="21" customFormat="1" ht="14" spans="1:11">
       <c r="A23" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C23" s="26" t="s">
+      <c r="B23" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C23" s="18" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="32">
@@ -2512,19 +2491,19 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K23" s="18">
+      <c r="K23" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" s="14" customFormat="1" ht="14" spans="1:12">
+    <row r="24" s="21" customFormat="1" ht="14" spans="1:11">
       <c r="A24" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C24" s="26" t="s">
+      <c r="B24" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C24" s="18" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="32">
@@ -2544,19 +2523,19 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" s="14" customFormat="1" ht="14" spans="1:12">
+    <row r="25" s="21" customFormat="1" ht="14" spans="1:11">
       <c r="A25" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C25" s="26" t="s">
+      <c r="B25" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C25" s="18" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="32">
@@ -2576,19 +2555,19 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K25" s="18">
+      <c r="K25" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" s="14" customFormat="1" ht="14" spans="1:12">
+    <row r="26" s="21" customFormat="1" ht="14" spans="1:11">
       <c r="A26" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C26" s="26" t="s">
+      <c r="B26" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C26" s="18" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="32">
@@ -2609,19 +2588,19 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K26" s="18">
+      <c r="K26" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" s="14" customFormat="1" ht="14" spans="1:12">
+    <row r="27" s="21" customFormat="1" ht="14" spans="1:11">
       <c r="A27" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C27" s="26" t="s">
+      <c r="B27" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C27" s="18" t="s">
         <v>7</v>
       </c>
       <c r="D27" s="32">
@@ -2641,28 +2620,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K27" s="18">
+      <c r="K27" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" s="13" customFormat="1" ht="17" spans="1:12">
-      <c r="A28" s="25" t="s">
+    <row r="28" s="13" customFormat="1" spans="1:11">
+      <c r="A28" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C28" s="26" t="s">
+      <c r="B28" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C28" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="19">
         <v>7.8846</v>
       </c>
-      <c r="G28" s="35" t="s">
+      <c r="G28" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="21">
         <v>7.88456817764754</v>
       </c>
       <c r="I28" s="13">
@@ -2673,65 +2652,62 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K28" s="18">
+      <c r="K28" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" s="15" customFormat="1" spans="1:12">
-      <c r="A29" s="36" t="s">
+    <row r="29" s="21" customFormat="1" spans="1:11">
+      <c r="A29" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="37">
-        <v>202608</v>
-      </c>
-      <c r="C29" s="37" t="s">
+      <c r="B29" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C29" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="38">
-        <v>28.4759</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="14" t="s">
+      <c r="D29" s="32">
+        <v>28.2278</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="14">
-        <v>28.4758804623615</v>
+      <c r="H29" s="21">
+        <v>28.2278486997605</v>
       </c>
       <c r="I29" s="13">
         <f t="shared" si="0"/>
-        <v>28.4759</v>
+        <v>28.2278</v>
       </c>
       <c r="J29" s="13" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K29" s="18">
+      <c r="K29" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="14"/>
-    </row>
-    <row r="30" s="13" customFormat="1" spans="1:12">
-      <c r="A30" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C30" s="26" t="s">
+    </row>
+    <row r="30" s="13" customFormat="1" spans="1:11">
+      <c r="A30" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C30" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="19">
         <v>21.1352</v>
       </c>
-      <c r="G30" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" s="14">
+      <c r="G30" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" s="21">
         <v>21.1352354235823</v>
       </c>
       <c r="I30" s="13">
@@ -2742,67 +2718,64 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K30" s="18">
+      <c r="K30" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" s="16" customFormat="1" spans="1:12">
-      <c r="A31" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="37">
-        <v>202608</v>
-      </c>
-      <c r="C31" s="37" t="s">
+    <row r="31" s="13" customFormat="1" spans="1:11">
+      <c r="A31" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="40">
-        <v>37.6147</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H31" s="14">
-        <v>37.6146582153707</v>
+      <c r="D31" s="19">
+        <v>30.9022</v>
+      </c>
+      <c r="E31" s="21"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" s="21">
+        <v>30.902178097405</v>
       </c>
       <c r="I31" s="13">
         <f t="shared" si="0"/>
-        <v>37.6147</v>
+        <v>30.9022</v>
       </c>
       <c r="J31" s="13" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K31" s="18">
+      <c r="K31" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="13"/>
-    </row>
-    <row r="32" s="13" customFormat="1" spans="1:12">
-      <c r="A32" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C32" s="26" t="s">
+    </row>
+    <row r="32" s="13" customFormat="1" spans="1:11">
+      <c r="A32" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C32" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="19">
         <v>29.3258</v>
       </c>
       <c r="E32" s="13"/>
       <c r="F32" s="13"/>
-      <c r="G32" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H32" s="14">
+      <c r="G32" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H32" s="21">
         <v>29.3257962159257</v>
       </c>
       <c r="I32" s="13">
@@ -2813,86 +2786,84 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K32" s="18">
+      <c r="K32" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A33" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C33" s="26" t="s">
+      <c r="A33" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C33" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="43">
-        <v>6.42934856836342</v>
+      <c r="D33" s="19">
+        <v>6.4293</v>
       </c>
       <c r="E33" s="13"/>
       <c r="F33" s="13"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="18"/>
-    </row>
-    <row r="34" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A34" s="42">
-        <v>1300</v>
-      </c>
-      <c r="B34" s="26">
-        <v>202608</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="43">
-        <v>36.8261107411533</v>
-      </c>
+      <c r="G33" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" s="13">
+        <v>6.42934856836342</v>
+      </c>
+      <c r="I33" s="13">
+        <f t="shared" si="0"/>
+        <v>6.4293</v>
+      </c>
+      <c r="J33" s="13" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K33" s="22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" s="13" customFormat="1" spans="1:11">
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="14"/>
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
-      <c r="K34" s="18"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="22"/>
     </row>
     <row r="35" s="13" customFormat="1" spans="1:11">
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
-      <c r="D35" s="17"/>
+      <c r="D35" s="14"/>
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="18"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="K35" s="22"/>
     </row>
     <row r="36" s="13" customFormat="1" spans="1:11">
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
-      <c r="D36" s="17"/>
+      <c r="D36" s="14"/>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
-      <c r="K36" s="18"/>
-    </row>
-    <row r="37" s="13" customFormat="1" spans="1:11">
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="18"/>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="E41" s="44"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="22"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="E40" s="20"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L34" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L33" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2903,6 +2874,82 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="9.5" style="13" customWidth="1"/>
+    <col min="2" max="2" width="13.3333333333333" style="12" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="12" customWidth="1"/>
+    <col min="4" max="4" width="27.0416666666667" style="14" customWidth="1"/>
+    <col min="5" max="5" width="8.83333333333333" style="13"/>
+    <col min="6" max="8" width="8.83333333333333" style="13" customWidth="1"/>
+    <col min="9" max="16384" width="8.83333333333333" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="12" customFormat="1" ht="12" customHeight="1" spans="1:5">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" s="13" customFormat="1" ht="14" spans="1:5">
+      <c r="A2" s="17">
+        <v>1300</v>
+      </c>
+      <c r="B2" s="18">
+        <v>202609</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="19">
+        <v>36.6576</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" s="13" customFormat="1" spans="1:5">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="14"/>
+    </row>
+    <row r="4" s="13" customFormat="1" spans="1:5">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="14"/>
+    </row>
+    <row r="5" s="13" customFormat="1" spans="1:5">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="14"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="E9" s="20"/>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E2" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="95" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S37"/>
@@ -2919,97 +2966,97 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J2">
         <v>4.0901</v>
       </c>
       <c r="M2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O2">
         <v>110</v>
       </c>
       <c r="P2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q2" t="str">
         <f>VLOOKUP(C2,型号!A:C,3,0)</f>
         <v>BM1368+</v>
       </c>
       <c r="R2">
-        <f>_xlfn.XLOOKUP(Q2,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q2,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>4.0901</v>
       </c>
       <c r="S2" s="6">
@@ -3019,44 +3066,44 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J3">
         <v>4.0901</v>
       </c>
       <c r="M3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O3">
         <v>110</v>
       </c>
       <c r="P3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q3" t="str">
         <f>VLOOKUP(C3,型号!A:C,3,0)</f>
         <v>BM1368+</v>
       </c>
       <c r="R3">
-        <f>_xlfn.XLOOKUP(Q3,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q3,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>4.0901</v>
       </c>
       <c r="S3" s="6">
@@ -3066,44 +3113,44 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J4">
         <v>5.0536</v>
       </c>
       <c r="M4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O4">
         <v>110</v>
       </c>
       <c r="P4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q4" t="str">
         <f>VLOOKUP(C4,型号!A:C,3,0)</f>
         <v>BM1368</v>
       </c>
       <c r="R4">
-        <f>_xlfn.XLOOKUP(Q4,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q4,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>5.0536</v>
       </c>
       <c r="S4" s="6">
@@ -3113,44 +3160,44 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5">
         <v>2.2925</v>
       </c>
       <c r="M5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O5">
         <v>110</v>
       </c>
       <c r="P5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q5" t="str">
         <f>VLOOKUP(C5,型号!A:C,3,0)</f>
         <v>BM2380</v>
       </c>
       <c r="R5">
-        <f>_xlfn.XLOOKUP(Q5,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q5,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>2.2925</v>
       </c>
       <c r="S5" s="6">
@@ -3160,44 +3207,44 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J6">
         <v>3.4712</v>
       </c>
       <c r="M6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O6">
         <v>110</v>
       </c>
       <c r="P6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q6" t="str">
         <f>VLOOKUP(C6,型号!A:C,3,0)</f>
         <v>BM2042</v>
       </c>
       <c r="R6">
-        <f>_xlfn.XLOOKUP(Q6,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q6,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>3.4712</v>
       </c>
       <c r="S6" s="6">
@@ -3207,44 +3254,44 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J7">
         <v>3.7914</v>
       </c>
       <c r="M7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O7">
         <v>110</v>
       </c>
       <c r="P7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q7" t="str">
         <f>VLOOKUP(C7,型号!A:C,3,0)</f>
         <v>BM1366</v>
       </c>
       <c r="R7">
-        <f>_xlfn.XLOOKUP(Q7,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q7,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>3.7914</v>
       </c>
       <c r="S7" s="6">
@@ -3254,44 +3301,44 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O8">
         <v>110</v>
       </c>
       <c r="P8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q8" t="str">
         <f>VLOOKUP(C8,型号!A:C,3,0)</f>
         <v>BM1370晶圆</v>
       </c>
       <c r="R8">
-        <f>_xlfn.XLOOKUP(Q8,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q8,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>1</v>
       </c>
       <c r="S8" s="6">
@@ -3301,44 +3348,44 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J9">
         <v>3.7914</v>
       </c>
       <c r="M9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O9">
         <v>110</v>
       </c>
       <c r="P9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q9" t="str">
         <f>VLOOKUP(C9,型号!A:C,3,0)</f>
         <v>BM1366</v>
       </c>
       <c r="R9">
-        <f>_xlfn.XLOOKUP(Q9,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q9,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>3.7914</v>
       </c>
       <c r="S9" s="6">
@@ -3348,44 +3395,44 @@
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J10" s="8">
         <v>8.4438</v>
       </c>
       <c r="M10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O10">
         <v>110</v>
       </c>
       <c r="P10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q10" t="str">
         <f>VLOOKUP(C10,型号!A:C,3,0)</f>
         <v>BM1370</v>
       </c>
       <c r="R10" s="9">
-        <f>_xlfn.XLOOKUP(Q10,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q10,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>8.4438</v>
       </c>
       <c r="S10" s="6">
@@ -3395,44 +3442,44 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O11">
         <v>110</v>
       </c>
       <c r="P11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q11" t="str">
         <f>VLOOKUP(C11,型号!A:C,3,0)</f>
         <v>BM2282晶圆</v>
       </c>
       <c r="R11">
-        <f>_xlfn.XLOOKUP(Q11,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q11,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>1</v>
       </c>
       <c r="S11" s="6">
@@ -3442,44 +3489,44 @@
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O12">
         <v>110</v>
       </c>
       <c r="P12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q12" t="str">
         <f>VLOOKUP(C12,型号!A:C,3,0)</f>
         <v>BM2282晶圆</v>
       </c>
       <c r="R12">
-        <f>_xlfn.XLOOKUP(Q12,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q12,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>1</v>
       </c>
       <c r="S12" s="6">
@@ -3489,44 +3536,44 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O13">
         <v>110</v>
       </c>
       <c r="P13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q13" t="str">
         <f>VLOOKUP(C13,型号!A:C,3,0)</f>
         <v>BM2282晶圆</v>
       </c>
       <c r="R13">
-        <f>_xlfn.XLOOKUP(Q13,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q13,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>1</v>
       </c>
       <c r="S13" s="6">
@@ -3536,44 +3583,44 @@
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J14">
         <v>4.0901</v>
       </c>
       <c r="M14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O14">
         <v>110</v>
       </c>
       <c r="P14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q14" t="str">
         <f>VLOOKUP(C14,型号!A:C,3,0)</f>
         <v>BM1368+</v>
       </c>
       <c r="R14">
-        <f>_xlfn.XLOOKUP(Q14,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q14,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>4.0901</v>
       </c>
       <c r="S14" s="6">
@@ -3583,44 +3630,44 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J15" s="8">
         <v>8.4438</v>
       </c>
       <c r="M15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O15">
         <v>110</v>
       </c>
       <c r="P15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q15" t="str">
         <f>VLOOKUP(C15,型号!A:C,3,0)</f>
         <v>BM1370</v>
       </c>
       <c r="R15" s="9">
-        <f>_xlfn.XLOOKUP(Q15,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q15,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>8.4438</v>
       </c>
       <c r="S15" s="6">
@@ -3630,44 +3677,44 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J16">
         <v>5.2113</v>
       </c>
       <c r="M16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O16">
         <v>110</v>
       </c>
       <c r="P16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q16" t="str">
         <f>VLOOKUP(C16,型号!A:C,3,0)</f>
         <v>BM1489</v>
       </c>
       <c r="R16">
-        <f>_xlfn.XLOOKUP(Q16,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q16,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>5.2113</v>
       </c>
       <c r="S16" s="6">
@@ -3677,44 +3724,44 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J17">
         <v>3.7914</v>
       </c>
       <c r="M17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O17">
         <v>110</v>
       </c>
       <c r="P17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q17" t="str">
         <f>VLOOKUP(C17,型号!A:C,3,0)</f>
         <v>BM1366</v>
       </c>
       <c r="R17">
-        <f>_xlfn.XLOOKUP(Q17,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q17,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>3.7914</v>
       </c>
       <c r="S17" s="6">
@@ -3724,44 +3771,44 @@
     </row>
     <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J18">
         <v>3.4712</v>
       </c>
       <c r="M18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O18">
         <v>110</v>
       </c>
       <c r="P18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q18" t="str">
         <f>VLOOKUP(C18,型号!A:C,3,0)</f>
         <v>BM2110</v>
       </c>
       <c r="R18">
-        <f>_xlfn.XLOOKUP(Q18,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q18,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>3.4712</v>
       </c>
       <c r="S18" s="6">
@@ -3771,44 +3818,44 @@
     </row>
     <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J19">
         <v>3.4712</v>
       </c>
       <c r="M19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O19">
         <v>110</v>
       </c>
       <c r="P19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q19" t="str">
         <f>VLOOKUP(C19,型号!A:C,3,0)</f>
         <v>BM2130</v>
       </c>
       <c r="R19">
-        <f>_xlfn.XLOOKUP(Q19,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q19,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>3.4712</v>
       </c>
       <c r="S19" s="6">
@@ -3818,44 +3865,44 @@
     </row>
     <row r="20" spans="1:19">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J20">
         <v>4.0901</v>
       </c>
       <c r="M20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O20">
         <v>110</v>
       </c>
       <c r="P20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q20" t="str">
         <f>VLOOKUP(C20,型号!A:C,3,0)</f>
         <v>BM1368+</v>
       </c>
       <c r="R20">
-        <f>_xlfn.XLOOKUP(Q20,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q20,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>4.0901</v>
       </c>
       <c r="S20" s="6">
@@ -3865,44 +3912,44 @@
     </row>
     <row r="21" spans="1:19">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J21">
         <v>2.9837</v>
       </c>
       <c r="M21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O21">
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q21" t="str">
         <f>VLOOKUP(C21,型号!A:C,3,0)</f>
         <v>BM2382</v>
       </c>
       <c r="R21">
-        <f>_xlfn.XLOOKUP(Q21,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q21,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>2.9837</v>
       </c>
       <c r="S21" s="6">
@@ -3912,44 +3959,44 @@
     </row>
     <row r="22" spans="1:19">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J22" s="8">
         <v>8.4438</v>
       </c>
       <c r="M22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O22">
         <v>110</v>
       </c>
       <c r="P22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q22" t="str">
         <f>VLOOKUP(C22,型号!A:C,3,0)</f>
         <v>BM1370</v>
       </c>
       <c r="R22" s="9">
-        <f>_xlfn.XLOOKUP(Q22,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q22,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>8.4438</v>
       </c>
       <c r="S22" s="6">
@@ -3959,44 +4006,44 @@
     </row>
     <row r="23" spans="1:19">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J23" s="8">
         <v>8.4438</v>
       </c>
       <c r="M23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O23">
         <v>110</v>
       </c>
       <c r="P23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q23" t="str">
         <f>VLOOKUP(C23,型号!A:C,3,0)</f>
         <v>BM1370</v>
       </c>
       <c r="R23" s="9">
-        <f>_xlfn.XLOOKUP(Q23,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q23,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>8.4438</v>
       </c>
       <c r="S23" s="6">
@@ -4006,44 +4053,44 @@
     </row>
     <row r="24" spans="1:19">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J24">
         <v>3.4712</v>
       </c>
       <c r="M24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O24">
         <v>110</v>
       </c>
       <c r="P24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q24" t="str">
         <f>VLOOKUP(C24,型号!A:C,3,0)</f>
         <v>BM1766</v>
       </c>
       <c r="R24">
-        <f>_xlfn.XLOOKUP(Q24,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q24,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>3.4712</v>
       </c>
       <c r="S24" s="6">
@@ -4053,44 +4100,44 @@
     </row>
     <row r="25" spans="1:19">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J25">
         <v>5.0536</v>
       </c>
       <c r="M25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O25">
         <v>110</v>
       </c>
       <c r="P25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q25" t="str">
         <f>VLOOKUP(C25,型号!A:C,3,0)</f>
         <v>BM1368</v>
       </c>
       <c r="R25">
-        <f>_xlfn.XLOOKUP(Q25,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q25,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>5.0536</v>
       </c>
       <c r="S25" s="6">
@@ -4100,44 +4147,44 @@
     </row>
     <row r="26" spans="1:19">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J26" s="8">
         <v>8.4438</v>
       </c>
       <c r="M26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O26">
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q26" t="str">
         <f>VLOOKUP(C26,型号!A:C,3,0)</f>
         <v>BM1370</v>
       </c>
       <c r="R26" s="9">
-        <f>_xlfn.XLOOKUP(Q26,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q26,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>8.4438</v>
       </c>
       <c r="S26" s="6">
@@ -4147,44 +4194,44 @@
     </row>
     <row r="27" spans="1:19">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J27" s="8">
         <v>8.4438</v>
       </c>
       <c r="M27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O27">
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q27" t="str">
         <f>VLOOKUP(C27,型号!A:C,3,0)</f>
         <v>BM1370</v>
       </c>
       <c r="R27" s="9">
-        <f>_xlfn.XLOOKUP(Q27,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q27,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>8.4438</v>
       </c>
       <c r="S27" s="6">
@@ -4194,44 +4241,44 @@
     </row>
     <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J28">
         <v>1490.092</v>
       </c>
       <c r="M28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O28">
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q28" t="str">
         <f>VLOOKUP(C28,型号!A:C,3,0)</f>
         <v>BM1368MD</v>
       </c>
       <c r="R28">
-        <f>_xlfn.XLOOKUP(Q28,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q28,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>1490.092</v>
       </c>
       <c r="S28" s="6">
@@ -4241,44 +4288,44 @@
     </row>
     <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J29">
         <v>11.2214</v>
       </c>
       <c r="M29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O29">
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q29" t="str">
         <f>VLOOKUP(C29,型号!A:C,3,0)</f>
         <v>BM2460</v>
       </c>
       <c r="R29">
-        <f>_xlfn.XLOOKUP(Q29,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q29,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>11.2214</v>
       </c>
       <c r="S29" s="6">
@@ -4288,44 +4335,44 @@
     </row>
     <row r="30" spans="1:19">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J30">
         <v>250.5673</v>
       </c>
       <c r="M30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O30">
         <v>110</v>
       </c>
       <c r="P30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q30" t="str">
         <f>VLOOKUP(C30,型号!A:C,3,0)</f>
         <v>BM2280</v>
       </c>
       <c r="R30">
-        <f>_xlfn.XLOOKUP(Q30,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q30,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>250.5673</v>
       </c>
       <c r="S30" s="6">
@@ -4335,44 +4382,44 @@
     </row>
     <row r="31" spans="1:19">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J31">
         <v>12.745</v>
       </c>
       <c r="M31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O31">
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q31" t="str">
         <f>VLOOKUP(C31,型号!A:C,3,0)</f>
         <v>BM1491</v>
       </c>
       <c r="R31">
-        <f>_xlfn.XLOOKUP(Q31,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q31,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>12.745</v>
       </c>
       <c r="S31" s="6">
@@ -4382,44 +4429,44 @@
     </row>
     <row r="32" spans="1:19">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J32" s="8">
         <v>8.4438</v>
       </c>
       <c r="M32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O32">
         <v>110</v>
       </c>
       <c r="P32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q32" t="str">
         <f>VLOOKUP(C32,型号!A:C,3,0)</f>
         <v>BM1370</v>
       </c>
       <c r="R32" s="9">
-        <f>_xlfn.XLOOKUP(Q32,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q32,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>8.4438</v>
       </c>
       <c r="S32" s="6">
@@ -4429,44 +4476,44 @@
     </row>
     <row r="33" spans="1:19">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J33">
         <v>31.8244</v>
       </c>
       <c r="M33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O33">
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q33" t="str">
         <f>VLOOKUP(C33,型号!A:C,3,0)</f>
         <v>BM1372</v>
       </c>
       <c r="R33">
-        <f>_xlfn.XLOOKUP(Q33,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q33,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>31.8244</v>
       </c>
       <c r="S33" s="6">
@@ -4476,44 +4523,44 @@
     </row>
     <row r="34" spans="1:19">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J34">
         <v>31.8244</v>
       </c>
       <c r="M34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O34">
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q34" t="str">
         <f>VLOOKUP(C34,型号!A:C,3,0)</f>
         <v>BM1372</v>
       </c>
       <c r="R34">
-        <f>_xlfn.XLOOKUP(Q34,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q34,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>31.8244</v>
       </c>
       <c r="S34" s="6">
@@ -4523,44 +4570,44 @@
     </row>
     <row r="35" spans="1:19">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J35">
         <v>7.8846</v>
       </c>
       <c r="M35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O35">
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q35" t="str">
         <f>VLOOKUP(C35,型号!A:C,3,0)</f>
         <v>BM2384</v>
       </c>
       <c r="R35">
-        <f>_xlfn.XLOOKUP(Q35,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q35,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>7.8846</v>
       </c>
       <c r="S35" s="6">
@@ -4570,44 +4617,44 @@
     </row>
     <row r="36" spans="1:19">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J36" s="8">
         <v>8.4438</v>
       </c>
       <c r="M36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O36">
         <v>110</v>
       </c>
       <c r="P36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q36" t="str">
         <f>VLOOKUP(C36,型号!A:C,3,0)</f>
         <v>BM1370</v>
       </c>
       <c r="R36" s="9">
-        <f>_xlfn.XLOOKUP(Q36,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q36,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>8.4438</v>
       </c>
       <c r="S36" s="6">
@@ -4617,44 +4664,44 @@
     </row>
     <row r="37" s="5" customFormat="1" spans="1:19">
       <c r="A37" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J37" s="8">
         <v>8.4438</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O37" s="5">
         <v>110</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q37" s="5" t="str">
         <f>VLOOKUP(C37,型号!A:C,3,0)</f>
         <v>BM1370</v>
       </c>
       <c r="R37" s="10">
-        <f>_xlfn.XLOOKUP(Q37,PO!A:A,PO!D:D,1,0)</f>
+        <f>_xlfn.XLOOKUP(Q37,chanhua芯片价格!A:A,chanhua芯片价格!D:D,1,0)</f>
         <v>8.4438</v>
       </c>
       <c r="S37" s="11">
@@ -4671,7 +4718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
@@ -4679,7 +4726,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -4688,7 +4735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
   <dimension ref="A2:S35"/>
@@ -4704,90 +4751,90 @@
   <sheetData>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" hidden="1" spans="1:19">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J3">
         <v>4.3874</v>
       </c>
       <c r="M3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O3">
         <v>220</v>
       </c>
       <c r="P3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q3" t="s">
         <v>10</v>
@@ -4802,37 +4849,37 @@
     </row>
     <row r="4" hidden="1" spans="1:19">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J4">
         <v>4.3874</v>
       </c>
       <c r="M4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O4">
         <v>220</v>
       </c>
       <c r="P4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q4" t="s">
         <v>10</v>
@@ -4847,37 +4894,37 @@
     </row>
     <row r="5" hidden="1" spans="1:19">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5">
         <v>5.4206</v>
       </c>
       <c r="M5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O5">
         <v>220</v>
       </c>
       <c r="P5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q5" t="s">
         <v>11</v>
@@ -4892,37 +4939,37 @@
     </row>
     <row r="6" hidden="1" spans="1:19">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J6">
         <v>2.2925</v>
       </c>
       <c r="M6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O6">
         <v>220</v>
       </c>
       <c r="P6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q6" t="s">
         <v>25</v>
@@ -4937,37 +4984,37 @@
     </row>
     <row r="7" hidden="1" spans="1:19">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J7">
         <v>3.4623</v>
       </c>
       <c r="M7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O7">
         <v>220</v>
       </c>
       <c r="P7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q7" t="s">
         <v>16</v>
@@ -4982,37 +5029,37 @@
     </row>
     <row r="8" hidden="1" spans="1:19">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J8">
         <v>4.0649</v>
       </c>
       <c r="M8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O8">
         <v>220</v>
       </c>
       <c r="P8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q8" t="s">
         <v>15</v>
@@ -5027,37 +5074,37 @@
     </row>
     <row r="9" hidden="1" spans="1:19">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O9">
         <v>220</v>
       </c>
       <c r="P9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q9" t="s">
         <v>26</v>
@@ -5072,37 +5119,37 @@
     </row>
     <row r="10" hidden="1" spans="1:19">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J10">
         <v>4.0649</v>
       </c>
       <c r="M10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O10">
         <v>220</v>
       </c>
       <c r="P10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q10" t="s">
         <v>15</v>
@@ -5117,37 +5164,37 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J11">
         <v>8.5529</v>
       </c>
       <c r="M11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O11">
         <v>220</v>
       </c>
       <c r="P11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q11" t="s">
         <v>26</v>
@@ -5162,40 +5209,40 @@
     </row>
     <row r="12" hidden="1" spans="1:19">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J12">
         <v>5033.56</v>
       </c>
       <c r="M12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O12">
         <v>220</v>
       </c>
       <c r="P12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -5207,40 +5254,40 @@
     </row>
     <row r="13" hidden="1" spans="1:19">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J13">
         <v>5033.56</v>
       </c>
       <c r="M13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O13">
         <v>220</v>
       </c>
       <c r="P13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -5252,40 +5299,40 @@
     </row>
     <row r="14" hidden="1" spans="1:19">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J14">
         <v>1500</v>
       </c>
       <c r="M14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O14">
         <v>220</v>
       </c>
       <c r="P14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -5297,37 +5344,37 @@
     </row>
     <row r="15" hidden="1" spans="1:19">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J15">
         <v>4.3874</v>
       </c>
       <c r="M15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O15">
         <v>220</v>
       </c>
       <c r="P15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q15" t="s">
         <v>10</v>
@@ -5342,37 +5389,37 @@
     </row>
     <row r="16" hidden="1" spans="1:19">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J16">
         <v>8.5529</v>
       </c>
       <c r="M16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O16">
         <v>220</v>
       </c>
       <c r="P16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q16" t="s">
         <v>26</v>
@@ -5387,37 +5434,37 @@
     </row>
     <row r="17" hidden="1" spans="1:19">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J17">
         <v>5.7392</v>
       </c>
       <c r="M17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O17">
         <v>220</v>
       </c>
       <c r="P17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q17" t="s">
         <v>14</v>
@@ -5432,37 +5479,37 @@
     </row>
     <row r="18" hidden="1" spans="1:19">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J18">
         <v>4.0649</v>
       </c>
       <c r="M18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O18">
         <v>220</v>
       </c>
       <c r="P18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q18" t="s">
         <v>15</v>
@@ -5477,37 +5524,37 @@
     </row>
     <row r="19" hidden="1" spans="1:19">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J19">
         <v>3.4623</v>
       </c>
       <c r="M19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O19">
         <v>220</v>
       </c>
       <c r="P19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q19" t="s">
         <v>16</v>
@@ -5522,37 +5569,37 @@
     </row>
     <row r="20" hidden="1" spans="1:19">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J20">
         <v>3.4623</v>
       </c>
       <c r="M20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O20">
         <v>220</v>
       </c>
       <c r="P20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q20" t="s">
         <v>16</v>
@@ -5567,37 +5614,37 @@
     </row>
     <row r="21" hidden="1" spans="1:19">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J21">
         <v>4.3874</v>
       </c>
       <c r="M21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O21">
         <v>220</v>
       </c>
       <c r="P21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q21" t="s">
         <v>10</v>
@@ -5612,37 +5659,37 @@
     </row>
     <row r="22" hidden="1" spans="1:19">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J22">
         <v>2.9793</v>
       </c>
       <c r="M22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O22">
         <v>220</v>
       </c>
       <c r="P22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q22" t="s">
         <v>27</v>
@@ -5657,37 +5704,37 @@
     </row>
     <row r="23" hidden="1" spans="1:19">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J23">
         <v>8.5529</v>
       </c>
       <c r="M23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O23">
         <v>220</v>
       </c>
       <c r="P23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q23" t="s">
         <v>26</v>
@@ -5702,37 +5749,37 @@
     </row>
     <row r="24" hidden="1" spans="1:19">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J24">
         <v>8.5529</v>
       </c>
       <c r="M24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O24">
         <v>220</v>
       </c>
       <c r="P24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q24" t="s">
         <v>26</v>
@@ -5747,37 +5794,37 @@
     </row>
     <row r="25" hidden="1" spans="1:19">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J25">
         <v>3.4623</v>
       </c>
       <c r="M25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O25">
         <v>220</v>
       </c>
       <c r="P25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q25" t="s">
         <v>16</v>
@@ -5792,37 +5839,37 @@
     </row>
     <row r="26" hidden="1" spans="1:19">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J26">
         <v>5.4206</v>
       </c>
       <c r="M26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O26">
         <v>220</v>
       </c>
       <c r="P26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q26" t="s">
         <v>11</v>
@@ -5837,37 +5884,37 @@
     </row>
     <row r="27" hidden="1" spans="1:19">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J27">
         <v>8.5529</v>
       </c>
       <c r="M27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O27">
         <v>220</v>
       </c>
       <c r="P27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q27" t="s">
         <v>26</v>
@@ -5882,37 +5929,37 @@
     </row>
     <row r="28" hidden="1" spans="1:19">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J28">
         <v>8.5529</v>
       </c>
       <c r="M28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O28">
         <v>220</v>
       </c>
       <c r="P28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q28" t="s">
         <v>26</v>
@@ -5927,37 +5974,37 @@
     </row>
     <row r="29" hidden="1" spans="1:19">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J29">
         <v>1080.1792</v>
       </c>
       <c r="M29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O29">
         <v>220</v>
       </c>
       <c r="P29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q29" t="s">
         <v>31</v>
@@ -5972,37 +6019,37 @@
     </row>
     <row r="30" hidden="1" spans="1:19">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J30">
         <v>11.7402</v>
       </c>
       <c r="M30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O30">
         <v>220</v>
       </c>
       <c r="P30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q30" t="s">
         <v>30</v>
@@ -6017,37 +6064,37 @@
     </row>
     <row r="31" hidden="1" spans="1:19">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J31">
         <v>250.5673</v>
       </c>
       <c r="M31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O31">
         <v>220</v>
       </c>
       <c r="P31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q31" t="s">
         <v>22</v>
@@ -6062,37 +6109,37 @@
     </row>
     <row r="32" hidden="1" spans="1:19">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J32">
         <v>11.2528</v>
       </c>
       <c r="M32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O32">
         <v>220</v>
       </c>
       <c r="P32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q32" t="s">
         <v>28</v>
@@ -6107,37 +6154,37 @@
     </row>
     <row r="33" hidden="1" spans="1:19">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J33">
         <v>8.5529</v>
       </c>
       <c r="M33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O33">
         <v>220</v>
       </c>
       <c r="P33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q33" t="s">
         <v>26</v>
@@ -6152,37 +6199,37 @@
     </row>
     <row r="34" hidden="1" spans="1:19">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J34">
         <v>31.5585</v>
       </c>
       <c r="M34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O34">
         <v>220</v>
       </c>
       <c r="P34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q34" t="s">
         <v>29</v>
@@ -6197,37 +6244,37 @@
     </row>
     <row r="35" hidden="1" spans="1:19">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J35">
         <v>31.5585</v>
       </c>
       <c r="M35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O35">
         <v>220</v>
       </c>
       <c r="P35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q35" t="e">
         <v>#N/A</v>
@@ -6254,7 +6301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
   <dimension ref="A2:BD20"/>
@@ -6267,169 +6314,169 @@
   <sheetData>
     <row r="2" spans="1:56">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" t="s">
+        <v>149</v>
+      </c>
+      <c r="L2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O2" t="s">
+        <v>153</v>
+      </c>
+      <c r="P2" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R2" t="s">
+        <v>156</v>
+      </c>
+      <c r="S2" t="s">
+        <v>157</v>
+      </c>
+      <c r="T2" t="s">
+        <v>158</v>
+      </c>
+      <c r="U2" t="s">
+        <v>159</v>
+      </c>
+      <c r="V2" t="s">
+        <v>160</v>
+      </c>
+      <c r="W2" t="s">
+        <v>161</v>
+      </c>
+      <c r="X2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>167</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>168</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>171</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>173</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>174</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AL2" t="s">
         <v>145</v>
       </c>
-      <c r="G2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K2" t="s">
-        <v>148</v>
-      </c>
-      <c r="L2" t="s">
-        <v>149</v>
-      </c>
-      <c r="M2" t="s">
-        <v>150</v>
-      </c>
-      <c r="N2" t="s">
-        <v>151</v>
-      </c>
-      <c r="O2" t="s">
-        <v>152</v>
-      </c>
-      <c r="P2" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>154</v>
-      </c>
-      <c r="R2" t="s">
-        <v>155</v>
-      </c>
-      <c r="S2" t="s">
-        <v>156</v>
-      </c>
-      <c r="T2" t="s">
-        <v>157</v>
-      </c>
-      <c r="U2" t="s">
-        <v>158</v>
-      </c>
-      <c r="V2" t="s">
-        <v>159</v>
-      </c>
-      <c r="W2" t="s">
-        <v>160</v>
-      </c>
-      <c r="X2" t="s">
-        <v>161</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>164</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>165</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>168</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>171</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>172</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>173</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>144</v>
-      </c>
       <c r="AM2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AN2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AO2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AP2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AQ2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AR2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AS2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AT2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AU2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AV2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AW2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AX2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AY2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AZ2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BA2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BB2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BC2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BD2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:56">
@@ -6440,10 +6487,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F3" s="1">
         <v>8.5278</v>
@@ -6452,13 +6499,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K3" s="1" t="e">
         <f>VLOOKUP(D3,#REF!,15,0)</f>
@@ -6468,7 +6515,7 @@
         <v>8.5278</v>
       </c>
       <c r="M3" s="1" t="e">
-        <f>VLOOKUP(K3,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K3,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N3" s="2" t="e">
@@ -6476,22 +6523,22 @@
         <v>#REF!</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X3" s="1">
         <v>0</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC3" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD3" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:56">
@@ -6502,10 +6549,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F4" s="1">
         <v>8.5278</v>
@@ -6514,13 +6561,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K4" s="1" t="e">
         <f>VLOOKUP(D4,#REF!,15,0)</f>
@@ -6530,7 +6577,7 @@
         <v>8.5278</v>
       </c>
       <c r="M4" s="1" t="e">
-        <f>VLOOKUP(K4,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K4,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N4" s="2" t="e">
@@ -6538,22 +6585,22 @@
         <v>#REF!</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X4" s="1">
         <v>0</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC4" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD4" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:56">
@@ -6564,10 +6611,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F5" s="1">
         <v>5.4151</v>
@@ -6576,13 +6623,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K5" s="1" t="e">
         <f>VLOOKUP(D5,#REF!,15,0)</f>
@@ -6592,7 +6639,7 @@
         <v>5.4151</v>
       </c>
       <c r="M5" s="1" t="e">
-        <f>VLOOKUP(K5,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K5,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N5" s="2" t="e">
@@ -6600,22 +6647,22 @@
         <v>#REF!</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X5" s="1">
         <v>0</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC5" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD5" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:56">
@@ -6626,10 +6673,10 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F6" s="1">
         <v>4.0649</v>
@@ -6638,13 +6685,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K6" s="1" t="e">
         <f>VLOOKUP(D6,#REF!,15,0)</f>
@@ -6654,7 +6701,7 @@
         <v>4.0649</v>
       </c>
       <c r="M6" s="1" t="e">
-        <f>VLOOKUP(K6,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K6,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N6" s="2" t="e">
@@ -6662,22 +6709,22 @@
         <v>#REF!</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X6" s="1">
         <v>0</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC6" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD6" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" hidden="1" spans="1:56">
@@ -6688,10 +6735,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F7">
         <v>4.382</v>
@@ -6700,13 +6747,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K7" t="e">
         <f>VLOOKUP(D7,#REF!,15,0)</f>
@@ -6716,7 +6763,7 @@
         <v>4.382</v>
       </c>
       <c r="M7" t="e">
-        <f>VLOOKUP(K7,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K7,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N7" s="3" t="e">
@@ -6724,22 +6771,22 @@
         <v>#REF!</v>
       </c>
       <c r="O7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:56">
@@ -6750,10 +6797,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F8" s="1">
         <v>8.5278</v>
@@ -6762,13 +6809,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K8" s="1" t="e">
         <f>VLOOKUP(D8,#REF!,15,0)</f>
@@ -6778,7 +6825,7 @@
         <v>8.5278</v>
       </c>
       <c r="M8" s="1" t="e">
-        <f>VLOOKUP(K8,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K8,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N8" s="2" t="e">
@@ -6786,22 +6833,22 @@
         <v>#REF!</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC8" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD8" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:56">
@@ -6812,10 +6859,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F9" s="1">
         <v>8.5278</v>
@@ -6824,13 +6871,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K9" s="1" t="e">
         <f>VLOOKUP(D9,#REF!,15,0)</f>
@@ -6840,7 +6887,7 @@
         <v>8.5278</v>
       </c>
       <c r="M9" s="1" t="e">
-        <f>VLOOKUP(K9,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K9,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N9" s="2" t="e">
@@ -6848,22 +6895,22 @@
         <v>#REF!</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X9" s="1">
         <v>0</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC9" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD9" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:56">
@@ -6874,10 +6921,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F10" s="1">
         <v>8.5278</v>
@@ -6886,13 +6933,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K10" s="1" t="e">
         <f>VLOOKUP(D10,#REF!,15,0)</f>
@@ -6902,7 +6949,7 @@
         <v>8.5278</v>
       </c>
       <c r="M10" s="1" t="e">
-        <f>VLOOKUP(K10,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K10,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N10" s="2" t="e">
@@ -6910,22 +6957,22 @@
         <v>#REF!</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X10" s="1">
         <v>0</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC10" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD10" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:56">
@@ -6936,10 +6983,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11" s="1">
         <v>5.4151</v>
@@ -6948,13 +6995,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K11" s="1" t="e">
         <f>VLOOKUP(D11,#REF!,15,0)</f>
@@ -6964,7 +7011,7 @@
         <v>5.4151</v>
       </c>
       <c r="M11" s="1" t="e">
-        <f>VLOOKUP(K11,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K11,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N11" s="2" t="e">
@@ -6972,22 +7019,22 @@
         <v>#REF!</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X11" s="1">
         <v>0</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC11" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD11" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" hidden="1" spans="1:56">
@@ -6998,10 +7045,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12">
         <v>5.4151</v>
@@ -7010,13 +7057,13 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K12" t="e">
         <f>VLOOKUP(D12,#REF!,15,0)</f>
@@ -7026,7 +7073,7 @@
         <v>5.4151</v>
       </c>
       <c r="M12" t="e">
-        <f>VLOOKUP(K12,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K12,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N12" s="3" t="e">
@@ -7034,22 +7081,22 @@
         <v>#REF!</v>
       </c>
       <c r="O12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X12">
         <v>0</v>
       </c>
       <c r="AC12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" hidden="1" spans="1:56">
@@ -7060,10 +7107,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F13">
         <v>4.382</v>
@@ -7072,13 +7119,13 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K13" t="e">
         <f>VLOOKUP(D13,#REF!,15,0)</f>
@@ -7088,7 +7135,7 @@
         <v>4.382</v>
       </c>
       <c r="M13" t="e">
-        <f>VLOOKUP(K13,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K13,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N13" s="3" t="e">
@@ -7096,22 +7143,22 @@
         <v>#REF!</v>
       </c>
       <c r="O13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X13">
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" hidden="1" spans="1:56">
@@ -7122,10 +7169,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F14">
         <v>4.382</v>
@@ -7134,13 +7181,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K14" t="e">
         <f>VLOOKUP(D14,#REF!,15,0)</f>
@@ -7150,7 +7197,7 @@
         <v>4.382</v>
       </c>
       <c r="M14" t="e">
-        <f>VLOOKUP(K14,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K14,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N14" s="3" t="e">
@@ -7158,22 +7205,22 @@
         <v>#REF!</v>
       </c>
       <c r="O14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:56">
@@ -7184,10 +7231,10 @@
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F15" s="1">
         <v>5.4151</v>
@@ -7196,13 +7243,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K15" s="1" t="e">
         <f>VLOOKUP(D15,#REF!,15,0)</f>
@@ -7212,7 +7259,7 @@
         <v>5.4151</v>
       </c>
       <c r="M15" s="1" t="e">
-        <f>VLOOKUP(K15,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K15,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N15" s="2" t="e">
@@ -7220,22 +7267,22 @@
         <v>#REF!</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X15" s="1">
         <v>0</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC15" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD15" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" hidden="1" spans="1:56">
@@ -7246,10 +7293,10 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16">
         <v>5.4151</v>
@@ -7258,13 +7305,13 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K16" t="e">
         <f>VLOOKUP(D16,#REF!,15,0)</f>
@@ -7274,7 +7321,7 @@
         <v>5.4151</v>
       </c>
       <c r="M16" t="e">
-        <f>VLOOKUP(K16,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K16,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N16" s="3" t="e">
@@ -7282,22 +7329,22 @@
         <v>#REF!</v>
       </c>
       <c r="O16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="AC16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:56">
@@ -7308,10 +7355,10 @@
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" s="1">
         <v>4.0649</v>
@@ -7320,13 +7367,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K17" s="1" t="e">
         <f>VLOOKUP(D17,#REF!,15,0)</f>
@@ -7336,7 +7383,7 @@
         <v>4.0649</v>
       </c>
       <c r="M17" s="1" t="e">
-        <f>VLOOKUP(K17,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K17,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N17" s="2" t="e">
@@ -7344,22 +7391,22 @@
         <v>#REF!</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X17" s="1">
         <v>0</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC17" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD17" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" hidden="1" spans="1:56">
@@ -7370,10 +7417,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F18">
         <v>4.382</v>
@@ -7382,13 +7429,13 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K18" t="e">
         <f>VLOOKUP(D18,#REF!,15,0)</f>
@@ -7398,7 +7445,7 @@
         <v>4.382</v>
       </c>
       <c r="M18" t="e">
-        <f>VLOOKUP(K18,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K18,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N18" s="3" t="e">
@@ -7406,22 +7453,22 @@
         <v>#REF!</v>
       </c>
       <c r="O18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X18">
         <v>0</v>
       </c>
       <c r="AC18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:56">
@@ -7432,10 +7479,10 @@
         <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F19" s="1">
         <v>4.0649</v>
@@ -7444,13 +7491,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K19" s="1" t="e">
         <f>VLOOKUP(D19,#REF!,15,0)</f>
@@ -7460,7 +7507,7 @@
         <v>4.0649</v>
       </c>
       <c r="M19" s="1" t="e">
-        <f>VLOOKUP(K19,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K19,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N19" s="2" t="e">
@@ -7468,22 +7515,22 @@
         <v>#REF!</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X19" s="1">
         <v>0</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC19" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD19" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" hidden="1" spans="1:56">
@@ -7494,10 +7541,10 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F20">
         <v>4.382</v>
@@ -7506,13 +7553,13 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K20" t="e">
         <f>VLOOKUP(D20,#REF!,15,0)</f>
@@ -7522,7 +7569,7 @@
         <v>4.382</v>
       </c>
       <c r="M20" t="e">
-        <f>VLOOKUP(K20,PO!A:D,4,0)</f>
+        <f>VLOOKUP(K20,chanhua芯片价格!A:D,4,0)</f>
         <v>#REF!</v>
       </c>
       <c r="N20" s="3" t="e">
@@ -7530,22 +7577,22 @@
         <v>#REF!</v>
       </c>
       <c r="O20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
       <c r="AC20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BC20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BD20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -7565,7 +7612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C37"/>
@@ -7577,21 +7624,21 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -7599,10 +7646,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7610,10 +7657,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
@@ -7621,10 +7668,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
         <v>25</v>
@@ -7632,10 +7679,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -7643,10 +7690,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -7654,21 +7701,21 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -7676,10 +7723,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -7687,43 +7734,43 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7731,10 +7778,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -7742,10 +7789,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -7753,10 +7800,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
@@ -7764,10 +7811,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -7775,10 +7822,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
@@ -7786,10 +7833,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -7797,10 +7844,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
@@ -7808,10 +7855,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
         <v>26</v>
@@ -7819,10 +7866,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
@@ -7830,10 +7877,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
@@ -7841,10 +7888,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -7852,10 +7899,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
         <v>26</v>
@@ -7863,10 +7910,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
         <v>26</v>
@@ -7874,10 +7921,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
@@ -7885,10 +7932,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s">
         <v>30</v>
@@ -7896,10 +7943,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
@@ -7907,10 +7954,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
         <v>28</v>
@@ -7918,10 +7965,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
         <v>26</v>
@@ -7929,10 +7976,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -7940,10 +7987,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -7951,10 +7998,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C35" t="s">
         <v>33</v>
@@ -7962,10 +8009,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -7973,10 +8020,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
